--- a/docs/Mapping_casi_uso/matrimoni/Matr_022.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_022.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3353" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3353" uniqueCount="285">
   <si>
     <t>Sezione</t>
   </si>
@@ -680,7 +680,10 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
+  </si>
+  <si>
+    <t>Firmatario</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -689,7 +692,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -698,7 +701,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Madre Sposa</t>
@@ -707,7 +710,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Tutore Sposo</t>
@@ -716,13 +719,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposo</t>
@@ -731,7 +734,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Tutore Sposa</t>
@@ -740,13 +743,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposa</t>
@@ -755,7 +758,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Estremi Certificazione</t>
@@ -824,13 +827,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -931,7 +934,7 @@
     <col min="4" max="4" width="59.5078125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.0546875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="114.08984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6528,10 +6531,10 @@
         <v>220</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>221</v>
@@ -6548,7 +6551,7 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>80</v>
@@ -6557,7 +6560,7 @@
         <v>9</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>82</v>
@@ -6566,12 +6569,12 @@
         <v>10</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>83</v>
@@ -6580,7 +6583,7 @@
         <v>42</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>84</v>
@@ -6589,12 +6592,12 @@
         <v>10</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>85</v>
@@ -6603,7 +6606,7 @@
         <v>9</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>86</v>
@@ -6612,12 +6615,12 @@
         <v>10</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>87</v>
@@ -6626,7 +6629,7 @@
         <v>42</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>88</v>
@@ -6635,12 +6638,12 @@
         <v>10</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>89</v>
@@ -6649,7 +6652,7 @@
         <v>9</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>90</v>
@@ -6658,12 +6661,12 @@
         <v>10</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>91</v>
@@ -6672,7 +6675,7 @@
         <v>9</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>92</v>
@@ -6681,12 +6684,12 @@
         <v>10</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>93</v>
@@ -6695,7 +6698,7 @@
         <v>42</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>94</v>
@@ -6704,12 +6707,12 @@
         <v>10</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>95</v>
@@ -6718,7 +6721,7 @@
         <v>42</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>96</v>
@@ -6727,12 +6730,12 @@
         <v>10</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>97</v>
@@ -6741,7 +6744,7 @@
         <v>42</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>98</v>
@@ -6750,12 +6753,12 @@
         <v>10</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>99</v>
@@ -6764,7 +6767,7 @@
         <v>9</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>100</v>
@@ -6773,12 +6776,12 @@
         <v>10</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>101</v>
@@ -6787,7 +6790,7 @@
         <v>9</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>102</v>
@@ -6796,12 +6799,12 @@
         <v>10</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>103</v>
@@ -6810,7 +6813,7 @@
         <v>9</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>104</v>
@@ -6819,12 +6822,12 @@
         <v>10</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>105</v>
@@ -6833,7 +6836,7 @@
         <v>9</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>106</v>
@@ -6842,12 +6845,12 @@
         <v>10</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>107</v>
@@ -6856,7 +6859,7 @@
         <v>9</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>108</v>
@@ -6865,12 +6868,12 @@
         <v>10</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>109</v>
@@ -6879,7 +6882,7 @@
         <v>42</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>110</v>
@@ -6888,12 +6891,12 @@
         <v>10</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>111</v>
@@ -6902,7 +6905,7 @@
         <v>42</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>112</v>
@@ -6911,12 +6914,12 @@
         <v>10</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>113</v>
@@ -6925,7 +6928,7 @@
         <v>9</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>114</v>
@@ -6934,12 +6937,12 @@
         <v>10</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>115</v>
@@ -6948,7 +6951,7 @@
         <v>9</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>116</v>
@@ -6957,12 +6960,12 @@
         <v>10</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>117</v>
@@ -6971,7 +6974,7 @@
         <v>9</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>118</v>
@@ -6980,12 +6983,12 @@
         <v>10</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>119</v>
@@ -6994,7 +6997,7 @@
         <v>9</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>120</v>
@@ -7003,12 +7006,12 @@
         <v>10</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>121</v>
@@ -7017,7 +7020,7 @@
         <v>9</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>122</v>
@@ -7026,12 +7029,12 @@
         <v>10</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>123</v>
@@ -7040,7 +7043,7 @@
         <v>9</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>124</v>
@@ -7049,12 +7052,12 @@
         <v>10</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>125</v>
@@ -7063,7 +7066,7 @@
         <v>9</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>126</v>
@@ -7072,12 +7075,12 @@
         <v>10</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>127</v>
@@ -7086,7 +7089,7 @@
         <v>9</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>128</v>
@@ -7095,12 +7098,12 @@
         <v>10</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>129</v>
@@ -7109,7 +7112,7 @@
         <v>9</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>130</v>
@@ -7118,12 +7121,12 @@
         <v>10</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>131</v>
@@ -7132,7 +7135,7 @@
         <v>42</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>132</v>
@@ -7141,12 +7144,12 @@
         <v>10</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>133</v>
@@ -7155,7 +7158,7 @@
         <v>42</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>134</v>
@@ -7164,21 +7167,21 @@
         <v>10</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B272" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B272" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="C272" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>136</v>
@@ -7187,12 +7190,12 @@
         <v>10</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>80</v>
@@ -7201,7 +7204,7 @@
         <v>9</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>82</v>
@@ -7210,12 +7213,12 @@
         <v>10</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>83</v>
@@ -7224,7 +7227,7 @@
         <v>42</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>84</v>
@@ -7233,12 +7236,12 @@
         <v>10</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>85</v>
@@ -7247,7 +7250,7 @@
         <v>9</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>86</v>
@@ -7256,12 +7259,12 @@
         <v>10</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>87</v>
@@ -7270,7 +7273,7 @@
         <v>42</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>88</v>
@@ -7279,12 +7282,12 @@
         <v>10</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>89</v>
@@ -7293,7 +7296,7 @@
         <v>9</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>90</v>
@@ -7302,12 +7305,12 @@
         <v>10</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>91</v>
@@ -7316,7 +7319,7 @@
         <v>9</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>92</v>
@@ -7325,12 +7328,12 @@
         <v>10</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>93</v>
@@ -7339,7 +7342,7 @@
         <v>42</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>94</v>
@@ -7348,12 +7351,12 @@
         <v>10</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>95</v>
@@ -7362,7 +7365,7 @@
         <v>42</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>96</v>
@@ -7371,12 +7374,12 @@
         <v>10</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>97</v>
@@ -7385,7 +7388,7 @@
         <v>42</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>98</v>
@@ -7394,12 +7397,12 @@
         <v>10</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>99</v>
@@ -7408,7 +7411,7 @@
         <v>9</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>100</v>
@@ -7417,12 +7420,12 @@
         <v>10</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>101</v>
@@ -7431,7 +7434,7 @@
         <v>9</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>102</v>
@@ -7440,12 +7443,12 @@
         <v>10</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>103</v>
@@ -7454,7 +7457,7 @@
         <v>9</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>104</v>
@@ -7463,12 +7466,12 @@
         <v>10</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>105</v>
@@ -7477,7 +7480,7 @@
         <v>9</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>106</v>
@@ -7486,12 +7489,12 @@
         <v>10</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>107</v>
@@ -7500,7 +7503,7 @@
         <v>9</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>108</v>
@@ -7509,12 +7512,12 @@
         <v>10</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>109</v>
@@ -7523,7 +7526,7 @@
         <v>42</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>110</v>
@@ -7532,12 +7535,12 @@
         <v>10</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>111</v>
@@ -7546,7 +7549,7 @@
         <v>42</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>112</v>
@@ -7555,12 +7558,12 @@
         <v>10</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>113</v>
@@ -7569,7 +7572,7 @@
         <v>9</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>114</v>
@@ -7578,12 +7581,12 @@
         <v>10</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>115</v>
@@ -7592,7 +7595,7 @@
         <v>9</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>116</v>
@@ -7601,12 +7604,12 @@
         <v>10</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>117</v>
@@ -7615,7 +7618,7 @@
         <v>9</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>118</v>
@@ -7624,12 +7627,12 @@
         <v>10</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>119</v>
@@ -7638,7 +7641,7 @@
         <v>9</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>120</v>
@@ -7647,12 +7650,12 @@
         <v>10</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>121</v>
@@ -7661,7 +7664,7 @@
         <v>9</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>122</v>
@@ -7670,12 +7673,12 @@
         <v>10</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>123</v>
@@ -7684,7 +7687,7 @@
         <v>9</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>124</v>
@@ -7693,12 +7696,12 @@
         <v>10</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>125</v>
@@ -7707,7 +7710,7 @@
         <v>9</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>126</v>
@@ -7716,12 +7719,12 @@
         <v>10</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>127</v>
@@ -7730,7 +7733,7 @@
         <v>9</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>128</v>
@@ -7739,12 +7742,12 @@
         <v>10</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>129</v>
@@ -7753,7 +7756,7 @@
         <v>9</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>130</v>
@@ -7762,12 +7765,12 @@
         <v>10</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>131</v>
@@ -7776,7 +7779,7 @@
         <v>42</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>132</v>
@@ -7785,12 +7788,12 @@
         <v>10</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>133</v>
@@ -7799,7 +7802,7 @@
         <v>42</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>134</v>
@@ -7808,21 +7811,21 @@
         <v>10</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>136</v>
@@ -7831,12 +7834,12 @@
         <v>10</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>80</v>
@@ -7845,7 +7848,7 @@
         <v>9</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>82</v>
@@ -7854,12 +7857,12 @@
         <v>10</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>83</v>
@@ -7868,7 +7871,7 @@
         <v>42</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>84</v>
@@ -7877,12 +7880,12 @@
         <v>10</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>85</v>
@@ -7891,7 +7894,7 @@
         <v>9</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>86</v>
@@ -7900,12 +7903,12 @@
         <v>10</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>87</v>
@@ -7914,7 +7917,7 @@
         <v>42</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>88</v>
@@ -7923,12 +7926,12 @@
         <v>10</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>89</v>
@@ -7937,7 +7940,7 @@
         <v>9</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>90</v>
@@ -7946,12 +7949,12 @@
         <v>10</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>91</v>
@@ -7960,7 +7963,7 @@
         <v>9</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>92</v>
@@ -7969,12 +7972,12 @@
         <v>10</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>93</v>
@@ -7983,7 +7986,7 @@
         <v>42</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>94</v>
@@ -7992,12 +7995,12 @@
         <v>10</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>95</v>
@@ -8006,7 +8009,7 @@
         <v>42</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>96</v>
@@ -8015,12 +8018,12 @@
         <v>10</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>97</v>
@@ -8029,7 +8032,7 @@
         <v>42</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>98</v>
@@ -8038,12 +8041,12 @@
         <v>10</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>99</v>
@@ -8052,7 +8055,7 @@
         <v>9</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>100</v>
@@ -8061,12 +8064,12 @@
         <v>10</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>101</v>
@@ -8075,7 +8078,7 @@
         <v>9</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>102</v>
@@ -8084,12 +8087,12 @@
         <v>10</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>103</v>
@@ -8098,7 +8101,7 @@
         <v>9</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>104</v>
@@ -8107,12 +8110,12 @@
         <v>10</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>105</v>
@@ -8121,7 +8124,7 @@
         <v>9</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>106</v>
@@ -8130,12 +8133,12 @@
         <v>10</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>107</v>
@@ -8144,7 +8147,7 @@
         <v>9</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>108</v>
@@ -8153,12 +8156,12 @@
         <v>10</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>109</v>
@@ -8167,7 +8170,7 @@
         <v>42</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>110</v>
@@ -8176,12 +8179,12 @@
         <v>10</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>111</v>
@@ -8190,7 +8193,7 @@
         <v>42</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>112</v>
@@ -8199,12 +8202,12 @@
         <v>10</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>113</v>
@@ -8213,7 +8216,7 @@
         <v>9</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>114</v>
@@ -8222,12 +8225,12 @@
         <v>10</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>115</v>
@@ -8236,7 +8239,7 @@
         <v>9</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>116</v>
@@ -8245,12 +8248,12 @@
         <v>10</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>117</v>
@@ -8259,7 +8262,7 @@
         <v>9</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>118</v>
@@ -8268,12 +8271,12 @@
         <v>10</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>119</v>
@@ -8282,7 +8285,7 @@
         <v>9</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>120</v>
@@ -8291,12 +8294,12 @@
         <v>10</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>121</v>
@@ -8305,7 +8308,7 @@
         <v>9</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>122</v>
@@ -8314,12 +8317,12 @@
         <v>10</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>123</v>
@@ -8328,7 +8331,7 @@
         <v>9</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>124</v>
@@ -8337,12 +8340,12 @@
         <v>10</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>125</v>
@@ -8351,7 +8354,7 @@
         <v>9</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>126</v>
@@ -8360,12 +8363,12 @@
         <v>10</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>127</v>
@@ -8374,7 +8377,7 @@
         <v>9</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>128</v>
@@ -8383,12 +8386,12 @@
         <v>10</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>129</v>
@@ -8397,7 +8400,7 @@
         <v>9</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>130</v>
@@ -8406,12 +8409,12 @@
         <v>10</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>131</v>
@@ -8420,7 +8423,7 @@
         <v>42</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>132</v>
@@ -8429,12 +8432,12 @@
         <v>10</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>133</v>
@@ -8443,7 +8446,7 @@
         <v>42</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>134</v>
@@ -8452,21 +8455,21 @@
         <v>10</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>136</v>
@@ -8475,12 +8478,12 @@
         <v>10</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>80</v>
@@ -8489,7 +8492,7 @@
         <v>9</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>82</v>
@@ -8498,12 +8501,12 @@
         <v>10</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>83</v>
@@ -8512,7 +8515,7 @@
         <v>42</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>84</v>
@@ -8521,12 +8524,12 @@
         <v>10</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>85</v>
@@ -8535,7 +8538,7 @@
         <v>9</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>86</v>
@@ -8544,12 +8547,12 @@
         <v>10</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>87</v>
@@ -8558,7 +8561,7 @@
         <v>42</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>88</v>
@@ -8567,12 +8570,12 @@
         <v>10</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>89</v>
@@ -8581,7 +8584,7 @@
         <v>9</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>90</v>
@@ -8590,12 +8593,12 @@
         <v>10</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>91</v>
@@ -8604,7 +8607,7 @@
         <v>9</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>92</v>
@@ -8613,12 +8616,12 @@
         <v>10</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>93</v>
@@ -8627,7 +8630,7 @@
         <v>42</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>94</v>
@@ -8636,12 +8639,12 @@
         <v>10</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>95</v>
@@ -8650,7 +8653,7 @@
         <v>42</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>96</v>
@@ -8659,12 +8662,12 @@
         <v>10</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>97</v>
@@ -8673,7 +8676,7 @@
         <v>42</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>98</v>
@@ -8682,12 +8685,12 @@
         <v>10</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>99</v>
@@ -8696,7 +8699,7 @@
         <v>9</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>100</v>
@@ -8705,12 +8708,12 @@
         <v>10</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>101</v>
@@ -8719,7 +8722,7 @@
         <v>9</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>102</v>
@@ -8728,12 +8731,12 @@
         <v>10</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>103</v>
@@ -8742,7 +8745,7 @@
         <v>9</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>104</v>
@@ -8751,12 +8754,12 @@
         <v>10</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>105</v>
@@ -8765,7 +8768,7 @@
         <v>9</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>106</v>
@@ -8774,12 +8777,12 @@
         <v>10</v>
       </c>
       <c r="G341" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>107</v>
@@ -8788,7 +8791,7 @@
         <v>9</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>108</v>
@@ -8797,12 +8800,12 @@
         <v>10</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>109</v>
@@ -8811,7 +8814,7 @@
         <v>42</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>110</v>
@@ -8820,12 +8823,12 @@
         <v>10</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>111</v>
@@ -8834,7 +8837,7 @@
         <v>42</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>112</v>
@@ -8843,12 +8846,12 @@
         <v>10</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>113</v>
@@ -8857,7 +8860,7 @@
         <v>9</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>114</v>
@@ -8866,12 +8869,12 @@
         <v>10</v>
       </c>
       <c r="G345" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>115</v>
@@ -8880,7 +8883,7 @@
         <v>9</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>116</v>
@@ -8889,12 +8892,12 @@
         <v>10</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>117</v>
@@ -8903,7 +8906,7 @@
         <v>9</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>118</v>
@@ -8912,12 +8915,12 @@
         <v>10</v>
       </c>
       <c r="G347" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>119</v>
@@ -8926,7 +8929,7 @@
         <v>9</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>120</v>
@@ -8935,12 +8938,12 @@
         <v>10</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>121</v>
@@ -8949,7 +8952,7 @@
         <v>9</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>122</v>
@@ -8958,12 +8961,12 @@
         <v>10</v>
       </c>
       <c r="G349" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>123</v>
@@ -8972,7 +8975,7 @@
         <v>9</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>124</v>
@@ -8981,12 +8984,12 @@
         <v>10</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>125</v>
@@ -8995,7 +8998,7 @@
         <v>9</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>126</v>
@@ -9004,12 +9007,12 @@
         <v>10</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>127</v>
@@ -9018,7 +9021,7 @@
         <v>9</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>128</v>
@@ -9027,12 +9030,12 @@
         <v>10</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>129</v>
@@ -9041,7 +9044,7 @@
         <v>9</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>130</v>
@@ -9050,12 +9053,12 @@
         <v>10</v>
       </c>
       <c r="G353" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>131</v>
@@ -9064,7 +9067,7 @@
         <v>42</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>132</v>
@@ -9073,12 +9076,12 @@
         <v>10</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>133</v>
@@ -9087,7 +9090,7 @@
         <v>42</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>134</v>
@@ -9096,21 +9099,21 @@
         <v>10</v>
       </c>
       <c r="G355" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>136</v>
@@ -9119,12 +9122,12 @@
         <v>10</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>80</v>
@@ -9133,7 +9136,7 @@
         <v>9</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>82</v>
@@ -9142,12 +9145,12 @@
         <v>10</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>83</v>
@@ -9156,7 +9159,7 @@
         <v>42</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>84</v>
@@ -9165,12 +9168,12 @@
         <v>10</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>85</v>
@@ -9179,7 +9182,7 @@
         <v>9</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E359" s="2" t="s">
         <v>86</v>
@@ -9188,12 +9191,12 @@
         <v>10</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>87</v>
@@ -9202,7 +9205,7 @@
         <v>42</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>88</v>
@@ -9211,12 +9214,12 @@
         <v>10</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>89</v>
@@ -9225,7 +9228,7 @@
         <v>9</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>90</v>
@@ -9234,12 +9237,12 @@
         <v>10</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>91</v>
@@ -9248,7 +9251,7 @@
         <v>9</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>92</v>
@@ -9257,12 +9260,12 @@
         <v>10</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>93</v>
@@ -9271,7 +9274,7 @@
         <v>42</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>94</v>
@@ -9280,12 +9283,12 @@
         <v>10</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>95</v>
@@ -9294,7 +9297,7 @@
         <v>42</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>96</v>
@@ -9303,12 +9306,12 @@
         <v>10</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>97</v>
@@ -9317,7 +9320,7 @@
         <v>42</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E365" s="2" t="s">
         <v>98</v>
@@ -9326,12 +9329,12 @@
         <v>10</v>
       </c>
       <c r="G365" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>99</v>
@@ -9340,7 +9343,7 @@
         <v>9</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>100</v>
@@ -9349,12 +9352,12 @@
         <v>10</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>101</v>
@@ -9363,7 +9366,7 @@
         <v>9</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E367" s="2" t="s">
         <v>102</v>
@@ -9372,12 +9375,12 @@
         <v>10</v>
       </c>
       <c r="G367" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>103</v>
@@ -9386,7 +9389,7 @@
         <v>9</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>104</v>
@@ -9395,12 +9398,12 @@
         <v>10</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>105</v>
@@ -9409,7 +9412,7 @@
         <v>9</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E369" s="2" t="s">
         <v>106</v>
@@ -9418,12 +9421,12 @@
         <v>10</v>
       </c>
       <c r="G369" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>107</v>
@@ -9432,7 +9435,7 @@
         <v>9</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>108</v>
@@ -9441,12 +9444,12 @@
         <v>10</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>109</v>
@@ -9455,7 +9458,7 @@
         <v>42</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E371" s="2" t="s">
         <v>110</v>
@@ -9464,12 +9467,12 @@
         <v>10</v>
       </c>
       <c r="G371" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>111</v>
@@ -9478,7 +9481,7 @@
         <v>42</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E372" s="2" t="s">
         <v>112</v>
@@ -9487,12 +9490,12 @@
         <v>10</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>113</v>
@@ -9501,7 +9504,7 @@
         <v>9</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E373" s="2" t="s">
         <v>114</v>
@@ -9510,12 +9513,12 @@
         <v>10</v>
       </c>
       <c r="G373" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>115</v>
@@ -9524,7 +9527,7 @@
         <v>9</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E374" s="2" t="s">
         <v>116</v>
@@ -9533,12 +9536,12 @@
         <v>10</v>
       </c>
       <c r="G374" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>117</v>
@@ -9547,7 +9550,7 @@
         <v>9</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E375" s="2" t="s">
         <v>118</v>
@@ -9556,12 +9559,12 @@
         <v>10</v>
       </c>
       <c r="G375" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>119</v>
@@ -9570,7 +9573,7 @@
         <v>9</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E376" s="2" t="s">
         <v>120</v>
@@ -9579,12 +9582,12 @@
         <v>10</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>121</v>
@@ -9593,7 +9596,7 @@
         <v>9</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E377" s="2" t="s">
         <v>122</v>
@@ -9602,12 +9605,12 @@
         <v>10</v>
       </c>
       <c r="G377" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>123</v>
@@ -9616,7 +9619,7 @@
         <v>9</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E378" s="2" t="s">
         <v>124</v>
@@ -9625,12 +9628,12 @@
         <v>10</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>125</v>
@@ -9639,7 +9642,7 @@
         <v>9</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E379" s="2" t="s">
         <v>126</v>
@@ -9648,12 +9651,12 @@
         <v>10</v>
       </c>
       <c r="G379" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>127</v>
@@ -9662,7 +9665,7 @@
         <v>9</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>128</v>
@@ -9671,12 +9674,12 @@
         <v>10</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>129</v>
@@ -9685,7 +9688,7 @@
         <v>9</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E381" s="2" t="s">
         <v>130</v>
@@ -9694,12 +9697,12 @@
         <v>10</v>
       </c>
       <c r="G381" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>131</v>
@@ -9708,7 +9711,7 @@
         <v>42</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>132</v>
@@ -9717,12 +9720,12 @@
         <v>10</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>133</v>
@@ -9731,7 +9734,7 @@
         <v>42</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E383" s="2" t="s">
         <v>134</v>
@@ -9740,21 +9743,21 @@
         <v>10</v>
       </c>
       <c r="G383" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E384" s="2" t="s">
         <v>136</v>
@@ -9763,12 +9766,12 @@
         <v>10</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>184</v>
@@ -9777,7 +9780,7 @@
         <v>42</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E385" s="2" t="s">
         <v>186</v>
@@ -9786,12 +9789,12 @@
         <v>10</v>
       </c>
       <c r="G385" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>188</v>
@@ -9800,7 +9803,7 @@
         <v>42</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E386" s="2" t="s">
         <v>189</v>
@@ -9809,12 +9812,12 @@
         <v>10</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>190</v>
@@ -9823,7 +9826,7 @@
         <v>42</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E387" s="2" t="s">
         <v>191</v>
@@ -9832,12 +9835,12 @@
         <v>10</v>
       </c>
       <c r="G387" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>192</v>
@@ -9846,7 +9849,7 @@
         <v>42</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E388" s="2" t="s">
         <v>193</v>
@@ -9855,12 +9858,12 @@
         <v>10</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>194</v>
@@ -9869,7 +9872,7 @@
         <v>42</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E389" s="2" t="s">
         <v>195</v>
@@ -9878,12 +9881,12 @@
         <v>10</v>
       </c>
       <c r="G389" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>196</v>
@@ -9892,7 +9895,7 @@
         <v>42</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E390" s="2" t="s">
         <v>197</v>
@@ -9901,12 +9904,12 @@
         <v>10</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>198</v>
@@ -9915,7 +9918,7 @@
         <v>42</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E391" s="2" t="s">
         <v>199</v>
@@ -9924,12 +9927,12 @@
         <v>10</v>
       </c>
       <c r="G391" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>80</v>
@@ -9938,7 +9941,7 @@
         <v>9</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E392" s="2" t="s">
         <v>82</v>
@@ -9947,12 +9950,12 @@
         <v>10</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>83</v>
@@ -9961,7 +9964,7 @@
         <v>42</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E393" s="2" t="s">
         <v>84</v>
@@ -9970,12 +9973,12 @@
         <v>10</v>
       </c>
       <c r="G393" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>85</v>
@@ -9984,7 +9987,7 @@
         <v>9</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E394" s="2" t="s">
         <v>86</v>
@@ -9993,12 +9996,12 @@
         <v>10</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>87</v>
@@ -10007,7 +10010,7 @@
         <v>42</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>88</v>
@@ -10016,12 +10019,12 @@
         <v>10</v>
       </c>
       <c r="G395" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>89</v>
@@ -10030,7 +10033,7 @@
         <v>9</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E396" s="2" t="s">
         <v>90</v>
@@ -10039,12 +10042,12 @@
         <v>10</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>91</v>
@@ -10053,7 +10056,7 @@
         <v>9</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>92</v>
@@ -10062,12 +10065,12 @@
         <v>10</v>
       </c>
       <c r="G397" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>93</v>
@@ -10076,7 +10079,7 @@
         <v>42</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>94</v>
@@ -10085,12 +10088,12 @@
         <v>10</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>95</v>
@@ -10099,7 +10102,7 @@
         <v>42</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E399" s="2" t="s">
         <v>96</v>
@@ -10108,12 +10111,12 @@
         <v>10</v>
       </c>
       <c r="G399" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>97</v>
@@ -10122,7 +10125,7 @@
         <v>42</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>98</v>
@@ -10131,12 +10134,12 @@
         <v>10</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>99</v>
@@ -10145,7 +10148,7 @@
         <v>9</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>100</v>
@@ -10154,12 +10157,12 @@
         <v>10</v>
       </c>
       <c r="G401" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>101</v>
@@ -10168,7 +10171,7 @@
         <v>9</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>102</v>
@@ -10177,12 +10180,12 @@
         <v>10</v>
       </c>
       <c r="G402" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>103</v>
@@ -10191,7 +10194,7 @@
         <v>9</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>104</v>
@@ -10200,12 +10203,12 @@
         <v>10</v>
       </c>
       <c r="G403" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>105</v>
@@ -10214,7 +10217,7 @@
         <v>9</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E404" s="2" t="s">
         <v>106</v>
@@ -10223,12 +10226,12 @@
         <v>10</v>
       </c>
       <c r="G404" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>107</v>
@@ -10237,7 +10240,7 @@
         <v>9</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>108</v>
@@ -10246,12 +10249,12 @@
         <v>10</v>
       </c>
       <c r="G405" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>109</v>
@@ -10260,7 +10263,7 @@
         <v>42</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E406" s="2" t="s">
         <v>110</v>
@@ -10269,12 +10272,12 @@
         <v>10</v>
       </c>
       <c r="G406" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>111</v>
@@ -10283,7 +10286,7 @@
         <v>42</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E407" s="2" t="s">
         <v>112</v>
@@ -10292,12 +10295,12 @@
         <v>10</v>
       </c>
       <c r="G407" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>113</v>
@@ -10306,7 +10309,7 @@
         <v>9</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>114</v>
@@ -10315,12 +10318,12 @@
         <v>10</v>
       </c>
       <c r="G408" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>115</v>
@@ -10329,7 +10332,7 @@
         <v>9</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E409" s="2" t="s">
         <v>116</v>
@@ -10338,12 +10341,12 @@
         <v>10</v>
       </c>
       <c r="G409" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>117</v>
@@ -10352,7 +10355,7 @@
         <v>9</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E410" s="2" t="s">
         <v>118</v>
@@ -10361,12 +10364,12 @@
         <v>10</v>
       </c>
       <c r="G410" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>119</v>
@@ -10375,7 +10378,7 @@
         <v>9</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E411" s="2" t="s">
         <v>120</v>
@@ -10384,12 +10387,12 @@
         <v>10</v>
       </c>
       <c r="G411" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>121</v>
@@ -10398,7 +10401,7 @@
         <v>9</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E412" s="2" t="s">
         <v>122</v>
@@ -10407,12 +10410,12 @@
         <v>10</v>
       </c>
       <c r="G412" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>123</v>
@@ -10421,7 +10424,7 @@
         <v>9</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>124</v>
@@ -10430,12 +10433,12 @@
         <v>10</v>
       </c>
       <c r="G413" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>125</v>
@@ -10444,7 +10447,7 @@
         <v>9</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E414" s="2" t="s">
         <v>126</v>
@@ -10453,12 +10456,12 @@
         <v>10</v>
       </c>
       <c r="G414" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>127</v>
@@ -10467,7 +10470,7 @@
         <v>9</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E415" s="2" t="s">
         <v>128</v>
@@ -10476,12 +10479,12 @@
         <v>10</v>
       </c>
       <c r="G415" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>129</v>
@@ -10490,7 +10493,7 @@
         <v>9</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>130</v>
@@ -10499,12 +10502,12 @@
         <v>10</v>
       </c>
       <c r="G416" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>131</v>
@@ -10513,7 +10516,7 @@
         <v>42</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E417" s="2" t="s">
         <v>132</v>
@@ -10522,12 +10525,12 @@
         <v>10</v>
       </c>
       <c r="G417" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>133</v>
@@ -10536,7 +10539,7 @@
         <v>42</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E418" s="2" t="s">
         <v>134</v>
@@ -10545,21 +10548,21 @@
         <v>10</v>
       </c>
       <c r="G418" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E419" s="2" t="s">
         <v>136</v>
@@ -10568,12 +10571,12 @@
         <v>10</v>
       </c>
       <c r="G419" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>80</v>
@@ -10582,7 +10585,7 @@
         <v>9</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E420" s="2" t="s">
         <v>82</v>
@@ -10591,12 +10594,12 @@
         <v>10</v>
       </c>
       <c r="G420" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>83</v>
@@ -10605,7 +10608,7 @@
         <v>42</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E421" s="2" t="s">
         <v>84</v>
@@ -10614,12 +10617,12 @@
         <v>10</v>
       </c>
       <c r="G421" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>85</v>
@@ -10628,7 +10631,7 @@
         <v>9</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E422" s="2" t="s">
         <v>86</v>
@@ -10637,12 +10640,12 @@
         <v>10</v>
       </c>
       <c r="G422" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>87</v>
@@ -10651,7 +10654,7 @@
         <v>42</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E423" s="2" t="s">
         <v>88</v>
@@ -10660,12 +10663,12 @@
         <v>10</v>
       </c>
       <c r="G423" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>89</v>
@@ -10674,7 +10677,7 @@
         <v>9</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E424" s="2" t="s">
         <v>90</v>
@@ -10683,12 +10686,12 @@
         <v>10</v>
       </c>
       <c r="G424" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>91</v>
@@ -10697,7 +10700,7 @@
         <v>9</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E425" s="2" t="s">
         <v>92</v>
@@ -10706,12 +10709,12 @@
         <v>10</v>
       </c>
       <c r="G425" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>93</v>
@@ -10720,7 +10723,7 @@
         <v>42</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E426" s="2" t="s">
         <v>94</v>
@@ -10729,12 +10732,12 @@
         <v>10</v>
       </c>
       <c r="G426" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>95</v>
@@ -10743,7 +10746,7 @@
         <v>42</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E427" s="2" t="s">
         <v>96</v>
@@ -10752,12 +10755,12 @@
         <v>10</v>
       </c>
       <c r="G427" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>97</v>
@@ -10766,7 +10769,7 @@
         <v>42</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E428" s="2" t="s">
         <v>98</v>
@@ -10775,12 +10778,12 @@
         <v>10</v>
       </c>
       <c r="G428" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>99</v>
@@ -10789,7 +10792,7 @@
         <v>9</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E429" s="2" t="s">
         <v>100</v>
@@ -10798,12 +10801,12 @@
         <v>10</v>
       </c>
       <c r="G429" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>101</v>
@@ -10812,7 +10815,7 @@
         <v>9</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E430" s="2" t="s">
         <v>102</v>
@@ -10821,12 +10824,12 @@
         <v>10</v>
       </c>
       <c r="G430" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>103</v>
@@ -10835,7 +10838,7 @@
         <v>9</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E431" s="2" t="s">
         <v>104</v>
@@ -10844,12 +10847,12 @@
         <v>10</v>
       </c>
       <c r="G431" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>105</v>
@@ -10858,7 +10861,7 @@
         <v>9</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>106</v>
@@ -10867,12 +10870,12 @@
         <v>10</v>
       </c>
       <c r="G432" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>107</v>
@@ -10881,7 +10884,7 @@
         <v>9</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E433" s="2" t="s">
         <v>108</v>
@@ -10890,12 +10893,12 @@
         <v>10</v>
       </c>
       <c r="G433" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>109</v>
@@ -10904,7 +10907,7 @@
         <v>42</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>110</v>
@@ -10913,12 +10916,12 @@
         <v>10</v>
       </c>
       <c r="G434" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>111</v>
@@ -10927,7 +10930,7 @@
         <v>42</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>112</v>
@@ -10936,12 +10939,12 @@
         <v>10</v>
       </c>
       <c r="G435" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>113</v>
@@ -10950,7 +10953,7 @@
         <v>9</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>114</v>
@@ -10959,12 +10962,12 @@
         <v>10</v>
       </c>
       <c r="G436" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>115</v>
@@ -10973,7 +10976,7 @@
         <v>9</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>116</v>
@@ -10982,12 +10985,12 @@
         <v>10</v>
       </c>
       <c r="G437" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>117</v>
@@ -10996,7 +10999,7 @@
         <v>9</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E438" s="2" t="s">
         <v>118</v>
@@ -11005,12 +11008,12 @@
         <v>10</v>
       </c>
       <c r="G438" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>119</v>
@@ -11019,7 +11022,7 @@
         <v>9</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>120</v>
@@ -11028,12 +11031,12 @@
         <v>10</v>
       </c>
       <c r="G439" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>121</v>
@@ -11042,7 +11045,7 @@
         <v>9</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>122</v>
@@ -11051,12 +11054,12 @@
         <v>10</v>
       </c>
       <c r="G440" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>123</v>
@@ -11065,7 +11068,7 @@
         <v>9</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E441" s="2" t="s">
         <v>124</v>
@@ -11074,12 +11077,12 @@
         <v>10</v>
       </c>
       <c r="G441" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>125</v>
@@ -11088,7 +11091,7 @@
         <v>9</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E442" s="2" t="s">
         <v>126</v>
@@ -11097,12 +11100,12 @@
         <v>10</v>
       </c>
       <c r="G442" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>127</v>
@@ -11111,7 +11114,7 @@
         <v>9</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>128</v>
@@ -11120,12 +11123,12 @@
         <v>10</v>
       </c>
       <c r="G443" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>129</v>
@@ -11134,7 +11137,7 @@
         <v>9</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>130</v>
@@ -11143,12 +11146,12 @@
         <v>10</v>
       </c>
       <c r="G444" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>131</v>
@@ -11157,7 +11160,7 @@
         <v>42</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E445" s="2" t="s">
         <v>132</v>
@@ -11166,12 +11169,12 @@
         <v>10</v>
       </c>
       <c r="G445" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>133</v>
@@ -11180,7 +11183,7 @@
         <v>42</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E446" s="2" t="s">
         <v>134</v>
@@ -11189,21 +11192,21 @@
         <v>10</v>
       </c>
       <c r="G446" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E447" s="2" t="s">
         <v>136</v>
@@ -11212,12 +11215,12 @@
         <v>10</v>
       </c>
       <c r="G447" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>184</v>
@@ -11226,7 +11229,7 @@
         <v>42</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>186</v>
@@ -11235,12 +11238,12 @@
         <v>10</v>
       </c>
       <c r="G448" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>188</v>
@@ -11249,7 +11252,7 @@
         <v>42</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>189</v>
@@ -11258,12 +11261,12 @@
         <v>10</v>
       </c>
       <c r="G449" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>190</v>
@@ -11272,7 +11275,7 @@
         <v>42</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>191</v>
@@ -11281,12 +11284,12 @@
         <v>10</v>
       </c>
       <c r="G450" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>192</v>
@@ -11295,7 +11298,7 @@
         <v>42</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>193</v>
@@ -11304,12 +11307,12 @@
         <v>10</v>
       </c>
       <c r="G451" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>194</v>
@@ -11318,7 +11321,7 @@
         <v>42</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>195</v>
@@ -11327,12 +11330,12 @@
         <v>10</v>
       </c>
       <c r="G452" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>196</v>
@@ -11341,7 +11344,7 @@
         <v>42</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E453" s="2" t="s">
         <v>197</v>
@@ -11350,12 +11353,12 @@
         <v>10</v>
       </c>
       <c r="G453" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>198</v>
@@ -11364,7 +11367,7 @@
         <v>42</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E454" s="2" t="s">
         <v>199</v>
@@ -11373,12 +11376,12 @@
         <v>10</v>
       </c>
       <c r="G454" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>190</v>
@@ -11387,7 +11390,7 @@
         <v>42</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E455" s="2" t="s">
         <v>191</v>
@@ -11401,19 +11404,19 @@
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B456" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C456" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D456" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C456" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D456" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="E456" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F456" s="2" t="s">
         <v>10</v>
@@ -11424,19 +11427,19 @@
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F457" s="2" t="s">
         <v>10</v>
@@ -11447,7 +11450,7 @@
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>107</v>
@@ -11456,10 +11459,10 @@
         <v>9</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F458" s="2" t="s">
         <v>10</v>
@@ -11470,7 +11473,7 @@
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>184</v>
@@ -11479,7 +11482,7 @@
         <v>42</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E459" s="2" t="s">
         <v>186</v>
@@ -11493,19 +11496,19 @@
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F460" s="2" t="s">
         <v>10</v>
@@ -11516,7 +11519,7 @@
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>188</v>
@@ -11525,7 +11528,7 @@
         <v>42</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E461" s="2" t="s">
         <v>189</v>
@@ -11539,7 +11542,7 @@
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>190</v>
@@ -11548,7 +11551,7 @@
         <v>42</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E462" s="2" t="s">
         <v>191</v>
@@ -11562,19 +11565,19 @@
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F463" s="2" t="s">
         <v>10</v>
@@ -11585,19 +11588,19 @@
     </row>
     <row r="464">
       <c r="A464" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F464" s="2" t="s">
         <v>10</v>
@@ -11608,7 +11611,7 @@
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>107</v>
@@ -11617,10 +11620,10 @@
         <v>9</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F465" s="2" t="s">
         <v>10</v>
@@ -11631,7 +11634,7 @@
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>184</v>
@@ -11640,7 +11643,7 @@
         <v>42</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E466" s="2" t="s">
         <v>186</v>
@@ -11654,19 +11657,19 @@
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B467" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C467" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D467" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E467" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="B467" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C467" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D467" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E467" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="F467" s="2" t="s">
         <v>10</v>
@@ -11677,7 +11680,7 @@
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>188</v>
@@ -11686,7 +11689,7 @@
         <v>42</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E468" s="2" t="s">
         <v>189</v>
@@ -11700,10 +11703,10 @@
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>42</v>
@@ -11712,7 +11715,7 @@
         <v>65</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F469" s="2" t="s">
         <v>10</v>
@@ -11723,10 +11726,10 @@
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>42</v>
@@ -11735,7 +11738,7 @@
         <v>65</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F470" s="2" t="s">
         <v>10</v>
@@ -11746,10 +11749,10 @@
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>42</v>
@@ -11758,7 +11761,7 @@
         <v>65</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F471" s="2" t="s">
         <v>10</v>
@@ -11769,10 +11772,10 @@
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>42</v>
@@ -11781,7 +11784,7 @@
         <v>207</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F472" s="2" t="s">
         <v>10</v>
@@ -11792,10 +11795,10 @@
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C473" s="2" t="s">
         <v>42</v>
@@ -11804,7 +11807,7 @@
         <v>207</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F473" s="2" t="s">
         <v>10</v>
@@ -11815,10 +11818,10 @@
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>9</v>
@@ -11827,10 +11830,10 @@
         <v>65</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F474" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G474" s="2" t="s">
         <v>45</v>
@@ -11838,10 +11841,10 @@
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C475" s="2" t="s">
         <v>9</v>
@@ -11850,7 +11853,7 @@
         <v>65</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F475" s="2" t="s">
         <v>10</v>
@@ -11861,19 +11864,19 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F476" s="2" t="s">
         <v>10</v>
@@ -11884,19 +11887,19 @@
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F477" s="2" t="s">
         <v>10</v>
@@ -11907,19 +11910,19 @@
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F478" s="2" t="s">
         <v>10</v>
@@ -11930,19 +11933,19 @@
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F479" s="2" t="s">
         <v>10</v>
